--- a/data/out/variants/v1_original_lags/summary_v1_original_lags.xlsx
+++ b/data/out/variants/v1_original_lags/summary_v1_original_lags.xlsx
@@ -547,7 +547,7 @@
         <v>9634</v>
       </c>
       <c r="M2" t="n">
-        <v>0.07845640182495117</v>
+        <v>0.07483220100402832</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         <v>9634</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04898524284362793</v>
+        <v>0.05344176292419434</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         <v>9634</v>
       </c>
       <c r="M4" t="n">
-        <v>1.931322336196899</v>
+        <v>2.160996437072754</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
         <v>9634</v>
       </c>
       <c r="M5" t="n">
-        <v>18.47295355796814</v>
+        <v>17.46512746810913</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>9634</v>
       </c>
       <c r="M6" t="n">
-        <v>3.509952783584595</v>
+        <v>3.562172889709473</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -800,13 +800,13 @@
         <v>76.11288173331081</v>
       </c>
       <c r="G7" t="n">
-        <v>46450.36822264796</v>
+        <v>46450.36822264797</v>
       </c>
       <c r="H7" t="n">
         <v>215.5234748760514</v>
       </c>
       <c r="I7" t="n">
-        <v>11.44664109477408</v>
+        <v>11.44664109477409</v>
       </c>
       <c r="J7" t="n">
         <v>48168</v>
@@ -818,7 +818,7 @@
         <v>9634</v>
       </c>
       <c r="M7" t="n">
-        <v>1397.071375608444</v>
+        <v>1723.712077617645</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         <v>9634</v>
       </c>
       <c r="M8" t="n">
-        <v>1992.072069883347</v>
+        <v>777.2465877532959</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>9634</v>
       </c>
       <c r="M9" t="n">
-        <v>532.5946662425995</v>
+        <v>235.9116082191467</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>9634</v>
       </c>
       <c r="M10" t="n">
-        <v>7.820294857025146</v>
+        <v>2.705244302749634</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1018,23 +1018,23 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 483, 'learning_rate': 0.017521005745699564, 'max_depth': 3, 'subsample': 0.8115255487349188, 'colsample_bytree': 0.9594978089587153}</t>
+          <t>{'n_estimators': 939, 'learning_rate': 0.013867195223154412, 'max_depth': 3, 'subsample': 0.7110075745431226, 'colsample_bytree': 0.7382193800088281}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.8098878357479427</v>
+        <v>0.8081247157601399</v>
       </c>
       <c r="F11" t="n">
-        <v>78.60629409774201</v>
+        <v>79.43340175882871</v>
       </c>
       <c r="G11" t="n">
-        <v>47797.50490288193</v>
+        <v>48240.78393551468</v>
       </c>
       <c r="H11" t="n">
-        <v>218.6264048619972</v>
+        <v>219.6378472292849</v>
       </c>
       <c r="I11" t="n">
-        <v>11.85318763691967</v>
+        <v>12.02281975481014</v>
       </c>
       <c r="J11" t="n">
         <v>48168</v>
@@ -1046,7 +1046,7 @@
         <v>9634</v>
       </c>
       <c r="M11" t="n">
-        <v>314.7406966686249</v>
+        <v>142.1663582324982</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1073,23 +1073,23 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 201, 'learning_rate': 0.02770848357356518, 'num_leaves': 110, 'min_child_samples': 39}</t>
+          <t>{'n_estimators': 272, 'learning_rate': 0.01899888130311442, 'num_leaves': 61, 'min_child_samples': 41}</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.7946240850228472</v>
+        <v>0.7985228285097541</v>
       </c>
       <c r="F12" t="n">
-        <v>82.2538173927378</v>
+        <v>80.71773288166708</v>
       </c>
       <c r="G12" t="n">
-        <v>51635.07733276509</v>
+        <v>50654.86540543444</v>
       </c>
       <c r="H12" t="n">
-        <v>227.2335303883762</v>
+        <v>225.0663577823981</v>
       </c>
       <c r="I12" t="n">
-        <v>11.49279491435707</v>
+        <v>11.42668929676841</v>
       </c>
       <c r="J12" t="n">
         <v>48168</v>
@@ -1101,7 +1101,7 @@
         <v>9634</v>
       </c>
       <c r="M12" t="n">
-        <v>675.9509844779968</v>
+        <v>148.8616714477539</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1128,23 +1128,23 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>{'iterations': 406, 'learning_rate': 0.02237707692459191, 'depth': 4}</t>
+          <t>{'iterations': 910, 'learning_rate': 0.013646718331966805, 'depth': 4}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.8062091952457563</v>
+        <v>0.8049285482846884</v>
       </c>
       <c r="F13" t="n">
-        <v>81.32481780192884</v>
+        <v>81.20010947501491</v>
       </c>
       <c r="G13" t="n">
-        <v>48722.37911138376</v>
+        <v>49044.35603296226</v>
       </c>
       <c r="H13" t="n">
-        <v>220.7314638002108</v>
+        <v>221.4596036142083</v>
       </c>
       <c r="I13" t="n">
-        <v>12.54082975683278</v>
+        <v>12.52278853295836</v>
       </c>
       <c r="J13" t="n">
         <v>48168</v>
@@ -1156,7 +1156,7 @@
         <v>9634</v>
       </c>
       <c r="M13" t="n">
-        <v>508.2409110069275</v>
+        <v>170.9594819545746</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>0.7321414146579928</v>
       </c>
       <c r="F14" t="n">
-        <v>89.56254371793071</v>
+        <v>89.56254371793068</v>
       </c>
       <c r="G14" t="n">
         <v>67344.30748570607</v>
@@ -1211,7 +1211,7 @@
         <v>9634</v>
       </c>
       <c r="M14" t="n">
-        <v>583.6091568470001</v>
+        <v>179.8062465190887</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>-71.80454884646547</v>
+        <v>-71.80454884646549</v>
       </c>
     </row>
     <row r="15">
@@ -1268,7 +1268,7 @@
         <v>9634</v>
       </c>
       <c r="M15" t="n">
-        <v>62.57832622528076</v>
+        <v>20.29582834243774</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>9634</v>
       </c>
       <c r="M16" t="n">
-        <v>1839.889783382416</v>
+        <v>841.8324482440948</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
